--- a/artfynd/A 13190-2023 artfynd.xlsx
+++ b/artfynd/A 13190-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,11 +678,11 @@
         <v>130910617</v>
       </c>
       <c r="B2" t="n">
-        <v>58426</v>
+        <v>58497</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -778,6 +778,996 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>NVI och fågelinventering Härad skog</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>130910358</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Motorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>500953</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6543969</v>
+      </c>
+      <c r="S3" t="n">
+        <v>4</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Viby</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Sara Poppelaars</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>NVI och fågelinventering Härad skog</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>130910450</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Motorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>500901</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6543955</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Viby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Sara Poppelaars</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>NVI och fågelinventering Härad skog</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>130910454</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Motorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>500989</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6544033</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Viby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Sara Poppelaars</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>NVI och fågelinventering Härad skog</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>130910460</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Motorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>501012</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6543936</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Viby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Sara Poppelaars</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>NVI och fågelinventering Härad skog</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>130910523</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Motorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>500943</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6543962</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Viby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mattias Finndin</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>NVI och fågelinventering Härad skog</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130910613</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Motorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>500890</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6544001</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Viby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Mattias Finndin</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>NVI och fågelinventering Härad skog</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>130910620</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Getrikebergen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>501123</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6544104</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Viby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Mattias Finndin</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>NVI och fågelinventering Härad skog</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>130910458</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Motorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>501008</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6544018</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Viby</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Sara Poppelaars</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>NVI och fågelinventering Härad skog</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>130910527</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Motorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>501091</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6544054</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Viby</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Mattias Finndin</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
         <is>
           <t>NVI och fågelinventering Härad skog</t>
         </is>

--- a/artfynd/A 13190-2023 artfynd.xlsx
+++ b/artfynd/A 13190-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
           <t>NVI och fågelinventering Härad skog</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130910617</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
           <t>NVI och fågelinventering Härad skog</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130910358</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
           <t>NVI och fågelinventering Härad skog</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130910450</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1112,6 +1132,11 @@
           <t>NVI och fågelinventering Härad skog</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130910454</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1222,6 +1247,11 @@
           <t>NVI och fågelinventering Härad skog</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130910460</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1332,6 +1362,11 @@
           <t>NVI och fågelinventering Härad skog</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130910523</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1442,6 +1477,11 @@
           <t>NVI och fågelinventering Härad skog</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130910613</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1552,6 +1592,11 @@
           <t>NVI och fågelinventering Härad skog</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130910620</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1662,6 +1707,11 @@
           <t>NVI och fågelinventering Härad skog</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130910458</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1772,8 +1822,25 @@
           <t>NVI och fågelinventering Härad skog</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130910527</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>